--- a/job_application_forms/024_dental_assistant_job_application_form--job_application_forms.xlsx
+++ b/job_application_forms/024_dental_assistant_job_application_form--job_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Street Address</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>job_title</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Address</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Job Title</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Current or previous job title</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,453 +639,147 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>resume</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>resume</t>
+          <t>job_application</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Resume</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Job Application</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Are you interested in this job?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>job_application</t>
+          <t>experience</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Job Application</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Job Experience</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>How many years do you have?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>experience</t>
+          <t>available_start</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Experience</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Available Start</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Start date</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>available</t>
+          <t>available_end</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Available End</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>End time</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>available_end</t>
+          <t>message</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Available End</t>
+          <t>Message</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Message</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>agree</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Agree</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>agree_message</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Agree Message</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>first_name_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>last_name_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Last Name</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>email_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>phone_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>experience_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Experience</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>experience_3</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Experience</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>available_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>available_end_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Available End</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>message_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Message</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>agree_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Agree</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>message_3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Message</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +796,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +863,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_1_year'}</t>
+          <t>less_than_1_year</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 1 year'}</t>
+          <t>Less than 1 year</t>
         </is>
       </c>
     </row>
@@ -1182,12 +880,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'1-2_years'}</t>
+          <t>1-2_years</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '1-2 years'}</t>
+          <t>1-2 years</t>
         </is>
       </c>
     </row>
@@ -1199,12 +897,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'2-5_years'}</t>
+          <t>2-5_years</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '2-5 years'}</t>
+          <t>2-5 years</t>
         </is>
       </c>
     </row>
@@ -1216,216 +914,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_5_years'}</t>
+          <t>more_than_5_years</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'More than 5 years'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>agree_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'label':_true}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>agree_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'label':_false}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>experience_2_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'label':_'less_than_1_year'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'label': 'Less than 1 year'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>experience_2_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'label':_'1-2_years'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'label': '1-2 years'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>experience_2_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'label':_'2-5_years'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'label': '2-5 years'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>experience_2_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'label':_'more_than_5_years'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'label': 'More than 5 years'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>experience_3_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'label':_'less_than_1_year'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'label': 'Less than 1 year'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>experience_3_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'label':_'1-2_years'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'label': '1-2 years'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>experience_3_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'label':_'2-5_years'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'label': '2-5 years'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>experience_3_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'label':_'more_than_5_years'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'label': 'More than 5 years'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>agree_2_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'label':_true}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>agree_2_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'label':_false}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'label': False}</t>
+          <t>More than 5 years</t>
         </is>
       </c>
     </row>
